--- a/exports/APOLLOHOSP_full_report.xlsx
+++ b/exports/APOLLOHOSP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.93</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44578.55208333334</v>
+        <v>44579.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>4901</v>
+        <v>4536.75</v>
       </c>
       <c r="I2" t="n">
         <v>4824.6007805</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.18</v>
+        <v>-10.37</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>10.47</v>
       </c>
       <c r="M2" t="n">
         <v>0.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.39</v>
+        <v>5.79</v>
       </c>
       <c r="O2" t="n">
         <v>0.78</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.53</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>4635</v>
+        <v>4763.2</v>
       </c>
       <c r="I3" t="n">
         <v>4737.677965804412</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.17</v>
+        <v>-4.99</v>
       </c>
       <c r="L3" t="n">
         <v>8.23</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>11.16</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44641.55208333334</v>
+        <v>44642.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>4775</v>
+        <v>4616</v>
       </c>
       <c r="I4" t="n">
         <v>4627.659503588926</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>0.25</v>
+        <v>-3.09</v>
       </c>
       <c r="L4" t="n">
-        <v>4.03</v>
+        <v>6.03</v>
       </c>
       <c r="M4" t="n">
         <v>2.63</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44669.55208333334</v>
+        <v>44670.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>4565</v>
+        <v>4815.9</v>
       </c>
       <c r="I5" t="n">
         <v>4746.910941516998</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1</v>
+        <v>-4.33</v>
       </c>
       <c r="L5" t="n">
-        <v>4.59</v>
+        <v>4.77</v>
       </c>
       <c r="M5" t="n">
         <v>1.39</v>
       </c>
       <c r="N5" t="n">
-        <v>2.49</v>
+        <v>5.07</v>
       </c>
       <c r="O5" t="n">
         <v>-1.78</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.58</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44677.55208333334</v>
+        <v>44678.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>4630</v>
+        <v>4505.75</v>
       </c>
       <c r="I6" t="n">
         <v>4595.264466924188</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.86</v>
+        <v>-6.44</v>
       </c>
       <c r="L6" t="n">
-        <v>4.83</v>
+        <v>6.56</v>
       </c>
       <c r="M6" t="n">
         <v>0.97</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44707.55208333334</v>
+        <v>44708.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>3699</v>
+        <v>3790.35</v>
       </c>
       <c r="I7" t="n">
         <v>3745.910573900678</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>17.9</v>
+        <v>15.88</v>
       </c>
       <c r="L7" t="n">
         <v>3.4</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>12.68</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44714.55208333334</v>
+        <v>44715.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>3648</v>
+        <v>3586.9</v>
       </c>
       <c r="I8" t="n">
         <v>3638.621234233585</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.76</v>
+        <v>-5.37</v>
       </c>
       <c r="L8" t="n">
-        <v>5.73</v>
+        <v>6.44</v>
       </c>
       <c r="M8" t="n">
         <v>0.95</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.58</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>3812</v>
+        <v>3871.95</v>
       </c>
       <c r="I9" t="n">
         <v>3866.955485459312</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.28</v>
+        <v>-7.95</v>
       </c>
       <c r="L9" t="n">
         <v>9.34</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>6.82</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44784.55208333334</v>
+        <v>44785.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>4422.95</v>
+        <v>4285.3</v>
       </c>
       <c r="I10" t="n">
         <v>4288.532708998253</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K10" t="n">
-        <v>14.23</v>
+        <v>10.68</v>
       </c>
       <c r="L10" t="n">
         <v>2.28</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5</v>
+        <v>1.65</v>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.99</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.91</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>4234.95</v>
+        <v>4288.15</v>
       </c>
       <c r="I11" t="n">
         <v>4265.270596210067</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>1.17</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>2.52</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.03</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>4333</v>
+        <v>4298.15</v>
       </c>
       <c r="I12" t="n">
         <v>4318.074127603191</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>1.05</v>
+        <v>0.23</v>
       </c>
       <c r="L12" t="n">
         <v>1.29</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>4.98</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44823.55208333334</v>
+        <v>44824.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>4309</v>
+        <v>4561.75</v>
       </c>
       <c r="I13" t="n">
         <v>4472.04343001219</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.25</v>
+        <v>-6.13</v>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>6.37</v>
       </c>
       <c r="M13" t="n">
         <v>0.21</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>5.73</v>
       </c>
       <c r="O13" t="n">
         <v>-0.88</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>4424</v>
+        <v>4298.7</v>
       </c>
       <c r="I14" t="n">
         <v>4375.616097742572</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.02</v>
+        <v>-5.77</v>
       </c>
       <c r="L14" t="n">
-        <v>5.38</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>0.64</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>8.06</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44861.55208333334</v>
+        <v>44862.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>4440</v>
+        <v>4569.25</v>
       </c>
       <c r="I15" t="n">
         <v>4471.224202735957</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.29</v>
+        <v>-6.29</v>
       </c>
       <c r="L15" t="n">
-        <v>4.66</v>
+        <v>6.64</v>
       </c>
       <c r="M15" t="n">
         <v>1.63</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.26</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>4358</v>
+        <v>4271.85</v>
       </c>
       <c r="I16" t="n">
         <v>4348.408569339348</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.62</v>
+        <v>-6.51</v>
       </c>
       <c r="L16" t="n">
-        <v>5.09</v>
+        <v>6.68</v>
       </c>
       <c r="M16" t="n">
         <v>0.53</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.94</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44876.55208333334</v>
+        <v>44879.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>4413.6</v>
+        <v>4516.4</v>
       </c>
       <c r="I17" t="n">
         <v>4478.898378554687</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.32</v>
+        <v>-5.72</v>
       </c>
       <c r="L17" t="n">
-        <v>6.27</v>
+        <v>6.93</v>
       </c>
       <c r="M17" t="n">
         <v>2.39</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.67</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44910.55208333334</v>
+        <v>44911.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>4635</v>
+        <v>4597.3</v>
       </c>
       <c r="I18" t="n">
         <v>4611.185073492874</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
-        <v>2.63</v>
+        <v>1.79</v>
       </c>
       <c r="L18" t="n">
         <v>4.34</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>3.94</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>4726.8</v>
+        <v>4750</v>
       </c>
       <c r="I19" t="n">
         <v>4746.585518918955</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.82</v>
+        <v>-3.32</v>
       </c>
       <c r="L19" t="n">
-        <v>2.96</v>
+        <v>4.16</v>
       </c>
       <c r="M19" t="n">
         <v>0.88</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>4.23</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44923.55208333334</v>
+        <v>44924.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>4585.6</v>
+        <v>4514</v>
       </c>
       <c r="I20" t="n">
         <v>4578.574860693056</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.46</v>
+        <v>-4.97</v>
       </c>
       <c r="L20" t="n">
-        <v>3.54</v>
+        <v>5.72</v>
       </c>
       <c r="M20" t="n">
         <v>0.28</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.47</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44965.38541666666</v>
+        <v>44965.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>4385</v>
+        <v>4393.75</v>
       </c>
       <c r="I21" t="n">
         <v>4386.887892053004</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="L21" t="n">
         <v>2.13</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.78</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44994.55208333334</v>
+        <v>44995.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>4412.1</v>
+        <v>4314.3</v>
       </c>
       <c r="I22" t="n">
         <v>4372.1054049848</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>0.42</v>
+        <v>-1.81</v>
       </c>
       <c r="L22" t="n">
         <v>5.09</v>
@@ -1695,7 +1958,7 @@
         <v>1.93</v>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
         <v>2.15</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.77</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45028.55208333334</v>
+        <v>45029.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>4324.5</v>
+        <v>4440.65</v>
       </c>
       <c r="I23" t="n">
         <v>4368.801529749036</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.24</v>
+        <v>-2.93</v>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>3.87</v>
       </c>
       <c r="M23" t="n">
         <v>0.87</v>
       </c>
       <c r="N23" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="O23" t="n">
         <v>-2.2</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.13</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>4476</v>
+        <v>4459.35</v>
       </c>
       <c r="I24" t="n">
         <v>4474.004880213093</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="L24" t="n">
         <v>4.93</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.83</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45071.55208333334</v>
+        <v>45072.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>4583</v>
+        <v>4606.25</v>
       </c>
       <c r="I25" t="n">
         <v>4605.967075489257</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.77</v>
+        <v>-3.29</v>
       </c>
       <c r="L25" t="n">
         <v>3.62</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.66</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45138.55208333334</v>
+        <v>45139.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>5185</v>
+        <v>5042.55</v>
       </c>
       <c r="I26" t="n">
         <v>5080.816451547564</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K26" t="n">
-        <v>12.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>1.76</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.09</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45174.38541666666</v>
+        <v>45174.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>4970</v>
+        <v>4980</v>
       </c>
       <c r="I27" t="n">
         <v>4975.574006307882</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="L27" t="n">
         <v>3.32</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>3.37</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>4970</v>
+        <v>4847.2</v>
       </c>
       <c r="I28" t="n">
         <v>4935.644715516772</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>48</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.2</v>
+        <v>-2.67</v>
       </c>
       <c r="L28" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="M28" t="n">
         <v>1.17</v>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="O28" t="n">
         <v>3.04</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.25</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>4890</v>
+        <v>5135.5</v>
       </c>
       <c r="I29" t="n">
         <v>4963.227678416541</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.88</v>
+        <v>-5.95</v>
       </c>
       <c r="L29" t="n">
-        <v>2.56</v>
+        <v>6.12</v>
       </c>
       <c r="M29" t="n">
-        <v>0.63</v>
+        <v>1.24</v>
       </c>
       <c r="N29" t="n">
-        <v>1.71</v>
+        <v>5.28</v>
       </c>
       <c r="O29" t="n">
         <v>-2.41</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.44</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45272.55208333334</v>
+        <v>45273.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>5430.9</v>
+        <v>5378</v>
       </c>
       <c r="I30" t="n">
         <v>5410.049179947268</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K30" t="n">
-        <v>5.75</v>
+        <v>4.72</v>
       </c>
       <c r="L30" t="n">
         <v>3.86</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.45</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45282.55208333334</v>
+        <v>45286.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>5540</v>
+        <v>5627.3</v>
       </c>
       <c r="I31" t="n">
         <v>5617.271424935337</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.01</v>
+        <v>-4.64</v>
       </c>
       <c r="L31" t="n">
         <v>5.53</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.87</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>6617</v>
+        <v>6368.9</v>
       </c>
       <c r="I32" t="n">
         <v>6488.720729233933</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K32" t="n">
-        <v>17.59</v>
+        <v>13.18</v>
       </c>
       <c r="L32" t="n">
         <v>1.8</v>
@@ -2265,7 +2648,7 @@
         <v>0.67</v>
       </c>
       <c r="N32" t="n">
-        <v>2.53</v>
+        <v>3.85</v>
       </c>
       <c r="O32" t="n">
         <v>1.66</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.22</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>6170.1</v>
+        <v>6309.75</v>
       </c>
       <c r="I33" t="n">
         <v>6271.878622574844</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>3.12</v>
+        <v>0.93</v>
       </c>
       <c r="L33" t="n">
         <v>4.1</v>
@@ -2322,7 +2717,7 @@
         <v>1.14</v>
       </c>
       <c r="N33" t="n">
-        <v>2.37</v>
+        <v>3.16</v>
       </c>
       <c r="O33" t="n">
         <v>-3.85</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>5.39</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45400.38541666666</v>
+        <v>45400.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>6246.95</v>
+        <v>6100</v>
       </c>
       <c r="I34" t="n">
         <v>6237.288294698254</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-1</v>
+        <v>-3.32</v>
       </c>
       <c r="L34" t="n">
-        <v>3.13</v>
+        <v>4.07</v>
       </c>
       <c r="M34" t="n">
         <v>1.39</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.57</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>5949.65</v>
+        <v>6000</v>
       </c>
       <c r="I35" t="n">
         <v>5991.50310205523</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>2.46</v>
+        <v>1.64</v>
       </c>
       <c r="L35" t="n">
         <v>4.95</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.07</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>7135</v>
+        <v>6933.65</v>
       </c>
       <c r="I36" t="n">
         <v>6965.498985822614</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>116.1666666666667</v>
+        <v>118</v>
       </c>
       <c r="K36" t="n">
-        <v>18.92</v>
+        <v>15.56</v>
       </c>
       <c r="L36" t="n">
         <v>0.58</v>
@@ -2493,7 +2924,7 @@
         <v>1.22</v>
       </c>
       <c r="N36" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="O36" t="n">
         <v>1.1</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45579.38541666666</v>
+        <v>45579.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>7071.05</v>
+        <v>7086</v>
       </c>
       <c r="I37" t="n">
         <v>7083.668106139125</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.98</v>
+        <v>-2.2</v>
       </c>
       <c r="L37" t="n">
         <v>3.84</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.15</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45600.55208333334</v>
+        <v>45601.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>6950</v>
+        <v>6871</v>
       </c>
       <c r="I38" t="n">
         <v>6873.662937946314</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.92</v>
+        <v>-3.03</v>
       </c>
       <c r="L38" t="n">
         <v>4.12</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.17</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45602.55208333334</v>
+        <v>45603.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>6969.95</v>
+        <v>7424.25</v>
       </c>
       <c r="I39" t="n">
         <v>7157.447627639505</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.44</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>3.94</v>
+        <v>8.92</v>
       </c>
       <c r="M39" t="n">
-        <v>0.48</v>
+        <v>4.97</v>
       </c>
       <c r="N39" t="n">
-        <v>0.53</v>
+        <v>6.31</v>
       </c>
       <c r="O39" t="n">
         <v>0.53</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.03</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45608.38541666666</v>
+        <v>45608.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>7097.25</v>
+        <v>7010</v>
       </c>
       <c r="I40" t="n">
         <v>7041.102793669634</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.4</v>
+        <v>-5.58</v>
       </c>
       <c r="L40" t="n">
         <v>5.95</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>6.91</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>6902</v>
+        <v>7105.2</v>
       </c>
       <c r="I41" t="n">
         <v>7032.129655057505</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>1.54</v>
+        <v>-1.36</v>
       </c>
       <c r="L41" t="n">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="M41" t="n">
-        <v>0.25</v>
+        <v>1.13</v>
       </c>
       <c r="N41" t="n">
-        <v>2.31</v>
+        <v>3.09</v>
       </c>
       <c r="O41" t="n">
         <v>-2.03</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.46</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45665.38541666666</v>
+        <v>45665.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>7225</v>
+        <v>7135.05</v>
       </c>
       <c r="I42" t="n">
         <v>7156.770221795604</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>1.69</v>
+        <v>0.42</v>
       </c>
       <c r="L42" t="n">
         <v>4.13</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.66</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>6240.35</v>
+        <v>6388.5</v>
       </c>
       <c r="I43" t="n">
         <v>6298.365943103584</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>69</v>
+        <v>69.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>12.54</v>
+        <v>10.46</v>
       </c>
       <c r="L43" t="n">
         <v>1.33</v>
@@ -2892,7 +3407,7 @@
         <v>1.29</v>
       </c>
       <c r="N43" t="n">
-        <v>2.53</v>
+        <v>3.02</v>
       </c>
       <c r="O43" t="n">
         <v>-3.97</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>5.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>6902</v>
+        <v>6815</v>
       </c>
       <c r="I44" t="n">
         <v>6899.075034469937</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>8.039999999999999</v>
+        <v>6.68</v>
       </c>
       <c r="L44" t="n">
         <v>2.53</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>4.57</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45792.38541666666</v>
+        <v>45792.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>6940</v>
+        <v>7086.5</v>
       </c>
       <c r="I45" t="n">
         <v>6996.450957467284</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.83</v>
+        <v>-3.98</v>
       </c>
       <c r="L45" t="n">
-        <v>2.91</v>
+        <v>4.13</v>
       </c>
       <c r="M45" t="n">
         <v>1.04</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>5.13</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45810.55208333334</v>
+        <v>45811.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>6903</v>
+        <v>6806</v>
       </c>
       <c r="I46" t="n">
         <v>6867.535598239171</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.59</v>
+        <v>-3.96</v>
       </c>
       <c r="L46" t="n">
-        <v>3.29</v>
+        <v>4.05</v>
       </c>
       <c r="M46" t="n">
         <v>0.11</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>5.28</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45821.55208333334</v>
+        <v>45824.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>7000</v>
+        <v>7091</v>
       </c>
       <c r="I47" t="n">
         <v>7075.636153396798</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.85</v>
+        <v>-4.19</v>
       </c>
       <c r="L47" t="n">
-        <v>3.66</v>
+        <v>4.29</v>
       </c>
       <c r="M47" t="n">
         <v>0.68</v>
       </c>
       <c r="N47" t="n">
-        <v>0.89</v>
+        <v>1.49</v>
       </c>
       <c r="O47" t="n">
         <v>-1.41</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45848.38541666666</v>
+        <v>45848.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>7425.5</v>
+        <v>7351</v>
       </c>
       <c r="I48" t="n">
         <v>7371.065796212056</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>4.72</v>
+        <v>3.67</v>
       </c>
       <c r="L48" t="n">
         <v>2.52</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>3.51</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45863.38541666666</v>
+        <v>45863.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>7431</v>
+        <v>7474.5</v>
       </c>
       <c r="I49" t="n">
         <v>7446.235129025742</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.09</v>
+        <v>-1.68</v>
       </c>
       <c r="L49" t="n">
         <v>1.83</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>3.41</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>7260</v>
+        <v>7197</v>
       </c>
       <c r="I50" t="n">
         <v>7230.698930626315</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.87</v>
+        <v>-3.71</v>
       </c>
       <c r="L50" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="M50" t="n">
         <v>0.9399999999999999</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>3.92</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45881.55208333334</v>
+        <v>45882.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>7253</v>
+        <v>7702</v>
       </c>
       <c r="I51" t="n">
         <v>7344.039011808029</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.78</v>
+        <v>-7.02</v>
       </c>
       <c r="L51" t="n">
-        <v>1.71</v>
+        <v>7.25</v>
       </c>
       <c r="M51" t="n">
-        <v>0.15</v>
+        <v>2.07</v>
       </c>
       <c r="N51" t="n">
-        <v>2.1</v>
+        <v>7.96</v>
       </c>
       <c r="O51" t="n">
         <v>-1.1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.03</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45897.55208333334</v>
+        <v>45898.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>7726</v>
+        <v>7597.5</v>
       </c>
       <c r="I52" t="n">
         <v>7655.717392654831</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K52" t="n">
-        <v>0.31</v>
+        <v>-1.36</v>
       </c>
       <c r="L52" t="n">
         <v>4.06</v>
       </c>
       <c r="M52" t="n">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="N52" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="O52" t="n">
         <v>7.96</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.57</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45904.38541666666</v>
+        <v>45904.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>7883.5</v>
+        <v>7891</v>
       </c>
       <c r="I53" t="n">
         <v>7890.5733119529</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.76</v>
+        <v>-3.86</v>
       </c>
       <c r="L53" t="n">
-        <v>3.82</v>
+        <v>4.23</v>
       </c>
       <c r="M53" t="n">
         <v>0.58</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>2.93</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45923.38541666666</v>
+        <v>45923.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>7700</v>
+        <v>7685</v>
       </c>
       <c r="I54" t="n">
         <v>7692.247057061486</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.42</v>
+        <v>-2.61</v>
       </c>
       <c r="L54" t="n">
         <v>3.54</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>2.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45936.55208333334</v>
+        <v>45937.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>7636</v>
+        <v>7687.5</v>
       </c>
       <c r="I55" t="n">
         <v>7676.644323434326</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>0.64</v>
+        <v>-0.03</v>
       </c>
       <c r="L55" t="n">
         <v>0.59</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>3.79</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45960.55208333334</v>
+        <v>45961.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>7798.5</v>
+        <v>7679.5</v>
       </c>
       <c r="I56" t="n">
         <v>7769.855808809989</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K56" t="n">
-        <v>1.44</v>
+        <v>-0.1</v>
       </c>
       <c r="L56" t="n">
         <v>0.88</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.09</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46014.55208333334</v>
+        <v>46015.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>7075</v>
+        <v>7185.5</v>
       </c>
       <c r="I57" t="n">
         <v>7116.573784772205</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K57" t="n">
-        <v>7.87</v>
+        <v>6.43</v>
       </c>
       <c r="L57" t="n">
         <v>2.75</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>3.94</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>7082</v>
+        <v>6942</v>
       </c>
       <c r="I58" t="n">
         <v>6983.649097801222</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.44</v>
+        <v>-3.39</v>
       </c>
       <c r="L58" t="n">
-        <v>1.96</v>
+        <v>3.46</v>
       </c>
       <c r="M58" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="N58" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="O58" t="n">
         <v>1.51</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>3.94</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>7086.5</v>
+        <v>7328</v>
       </c>
       <c r="I59" t="n">
         <v>7183.494931739357</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.08</v>
+        <v>-5.56</v>
       </c>
       <c r="L59" t="n">
-        <v>3.01</v>
+        <v>5.7</v>
       </c>
       <c r="M59" t="n">
         <v>0.31</v>
       </c>
       <c r="N59" t="n">
-        <v>1.18</v>
+        <v>3.45</v>
       </c>
       <c r="O59" t="n">
         <v>-1.24</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.55</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>7230</v>
+        <v>7161</v>
       </c>
       <c r="I60" t="n">
         <v>7170.292025580603</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.34</v>
+        <v>-2.28</v>
       </c>
       <c r="L60" t="n">
         <v>5.16</v>
@@ -3861,7 +4580,7 @@
         <v>4.34</v>
       </c>
       <c r="N60" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="O60" t="n">
         <v>3.45</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>4.99</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>6923.5</v>
+        <v>7100</v>
       </c>
       <c r="I61" t="n">
         <v>7075.64502336815</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>3.32</v>
+        <v>0.85</v>
       </c>
       <c r="L61" t="n">
         <v>1.38</v>
       </c>
       <c r="M61" t="n">
-        <v>0.93</v>
+        <v>2.12</v>
       </c>
       <c r="N61" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="O61" t="n">
         <v>-1.55</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.35</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>7780</v>
+        <v>7526</v>
       </c>
       <c r="I62" t="n">
         <v>7603.257256385128</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>9.58</v>
+        <v>6</v>
       </c>
       <c r="L62" t="n">
         <v>1.49</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.37</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>7433.5</v>
+        <v>7599</v>
       </c>
       <c r="I63" t="n">
         <v>7547.813483979912</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>1.23</v>
+        <v>-0.97</v>
       </c>
       <c r="L63" t="n">
         <v>4.57</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.91</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>8180.5</v>
+        <v>8081</v>
       </c>
       <c r="I64" t="n">
         <v>8081.194022512687</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>68</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>7.65</v>
+        <v>6.34</v>
       </c>
       <c r="L64" t="n">
         <v>5.9</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>4.95</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>8314.5</v>
+        <v>8436</v>
       </c>
       <c r="I65" t="n">
         <v>8319.892859579757</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.89</v>
+        <v>-4.39</v>
       </c>
       <c r="L65" t="n">
-        <v>3.22</v>
+        <v>5.06</v>
       </c>
       <c r="M65" t="n">
         <v>0.07000000000000001</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.43</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46244.55208333334</v>
+        <v>46245.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>8890</v>
+        <v>8733</v>
       </c>
       <c r="I66" t="n">
         <v>8756.72073377438</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K66" t="n">
-        <v>5.38</v>
+        <v>3.52</v>
       </c>
       <c r="L66" t="n">
         <v>2.67</v>
@@ -4203,7 +4994,7 @@
         <v>1.24</v>
       </c>
       <c r="N66" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O66" t="n">
         <v>0.49</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.75</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46248.38541666666</v>
+        <v>46248.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>8874.5</v>
+        <v>8919</v>
       </c>
       <c r="I67" t="n">
         <v>8896.149568412649</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.62</v>
+        <v>-2.13</v>
       </c>
       <c r="L67" t="n">
         <v>2.94</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>4.77</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46294.38541666666</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>8765.5</v>
+        <v>8659</v>
       </c>
       <c r="I68" t="n">
         <v>8726.983207856865</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>45.83333333333334</v>
+        <v>46</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.72</v>
+        <v>-2.92</v>
       </c>
       <c r="L68" t="n">
         <v>3.67</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>4.4</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46322.55208333334</v>
+        <v>46323.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>7859.5</v>
+        <v>8064.5</v>
       </c>
       <c r="I69" t="n">
         <v>7970.200449376532</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>9.23</v>
+        <v>6.87</v>
       </c>
       <c r="L69" t="n">
         <v>1.29</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,12 @@
       <c r="Q70" t="n">
         <v>2</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6536,7 +7381,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="6">
@@ -6546,7 +7391,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6556,7 +7401,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>116.2</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8">
@@ -6566,7 +7411,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6576,7 +7421,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -6586,7 +7431,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="11">
@@ -6626,7 +7471,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.36</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="15">
@@ -6636,7 +7481,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -6646,7 +7491,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.62</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="17">
@@ -6656,7 +7501,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.92</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="18">
@@ -6666,7 +7511,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.1</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -6676,7 +7521,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="20">
@@ -6686,7 +7531,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.3</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="21">
@@ -6696,7 +7541,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.34</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="22">
@@ -6706,7 +7551,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -6716,7 +7561,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6726,7 +7571,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="25">
@@ -6736,7 +7581,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.34</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="26">
@@ -6746,7 +7591,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="27">
@@ -6756,7 +7601,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.63</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="28">
@@ -6766,7 +7611,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
